--- a/docs/assets/aks-landing-zone-checklist.xlsx
+++ b/docs/assets/aks-landing-zone-checklist.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,12 @@
     <font>
       <name val="Segoe UI"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,6 +140,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -501,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -561,65 +570,69 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Pick a topology (row 0c) — 'spoke' if you already have an ALZ hub, 'hub_and_spoke' to create a new hub this run, or 'standalone' for an isolated subscription. Standalone skips Decisions 3 and 4.</t>
+          <t xml:space="preserve">   - Use the 'Reference' column links to read the Microsoft Learn docs for any setting.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
+          <t xml:space="preserve">   - Use the 'Comments' column (yellow) to record why you chose a value — handy for your team and auditors.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Pick a topology (row 0c) — 'spoke' if you already have an ALZ hub, 'hub_and_spoke' to create a new hub this run, or 'standalone' for an isolated subscription. Standalone skips Decisions 3 and 4.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>2. Open 'Advanced Cluster Settings' only if you need to change cluster sizing, networking,</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Run the wizard and use the workbook as your reference:</t>
+          <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>3. Run the wizard and use the workbook as your reference:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">       Deploy-AKSLandingZone</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>What the wizard does</t>
         </is>
       </c>
     </row>
@@ -627,33 +640,33 @@
       <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>What the wizard does</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Phase C — your PRs in the new GitHub repo run plan/apply and deploy the cluster.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>GitHub tokens — scopes you need</t>
         </is>
       </c>
     </row>
@@ -661,26 +674,26 @@
       <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GitHub tokens — scopes you need</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Main token (always):    repo, workflow, admin:org (Members Read &amp; Write)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Runner token (if 9a is true):  admin:org (full)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Resource names you will see</t>
         </is>
       </c>
     </row>
@@ -688,56 +701,66 @@
       <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Resource names you will see</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
+          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
+          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
+          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Approver team:                aksapplz-prod-approvers</t>
         </is>
@@ -754,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -763,6 +786,8 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -775,7 +800,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fill in the yellow column. Each row matches one question the wizard will ask you.</t>
+          <t>Fill in the yellow columns. Each row matches one question the wizard will ask you. Use 'Reference' for the Microsoft Learn docs and 'Comments' for your own notes.</t>
         </is>
       </c>
     </row>
@@ -808,6 +833,16 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Your value</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Comments</t>
         </is>
       </c>
     </row>
@@ -822,6 +857,8 @@
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -853,6 +890,12 @@
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -877,6 +920,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -907,6 +956,12 @@
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -937,6 +992,12 @@
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr"/>
@@ -949,6 +1010,8 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -977,6 +1040,12 @@
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1006,6 +1075,12 @@
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1030,6 +1105,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr"/>
@@ -1042,6 +1123,8 @@
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1066,6 +1149,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1094,6 +1183,12 @@
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr"/>
@@ -1106,6 +1201,8 @@
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1134,6 +1231,12 @@
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1162,6 +1265,12 @@
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1190,6 +1299,12 @@
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1218,6 +1333,12 @@
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr"/>
@@ -1230,6 +1351,8 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1258,6 +1381,12 @@
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1286,6 +1415,12 @@
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1314,6 +1449,12 @@
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1342,6 +1483,12 @@
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1370,6 +1517,12 @@
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1398,6 +1551,12 @@
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1426,6 +1585,12 @@
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -1454,6 +1619,12 @@
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr"/>
@@ -1466,6 +1637,8 @@
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1494,6 +1667,12 @@
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1522,6 +1701,12 @@
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1551,6 +1736,12 @@
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1579,6 +1770,12 @@
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr"/>
@@ -1591,6 +1788,8 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1619,6 +1818,12 @@
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr"/>
@@ -1631,6 +1836,8 @@
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1659,6 +1866,12 @@
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -1687,6 +1900,12 @@
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1715,6 +1934,12 @@
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr"/>
@@ -1727,6 +1952,8 @@
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1756,6 +1983,12 @@
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -1785,6 +2018,12 @@
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr"/>
@@ -1797,6 +2036,8 @@
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -1825,6 +2066,12 @@
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -1853,6 +2100,12 @@
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -1877,6 +2130,12 @@
       </c>
       <c r="E48" s="9" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -1905,6 +2164,12 @@
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr"/>
@@ -1917,6 +2182,8 @@
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -1945,6 +2212,12 @@
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -1973,6 +2246,12 @@
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -2001,6 +2280,12 @@
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -2029,6 +2314,12 @@
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -2057,6 +2348,12 @@
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2085,6 +2382,12 @@
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2113,6 +2416,12 @@
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2141,6 +2450,12 @@
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -2169,6 +2484,12 @@
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2197,6 +2518,12 @@
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2225,6 +2552,12 @@
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -2253,6 +2586,12 @@
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2281,6 +2620,12 @@
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -2309,6 +2654,12 @@
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -2337,6 +2688,12 @@
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -2365,22 +2722,28 @@
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="25">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2459,6 +2822,59 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2469,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2477,6 +2893,8 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2519,6 +2937,16 @@
           <t>Your value</t>
         </is>
       </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2530,6 +2958,8 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -2554,6 +2984,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -2577,6 +3013,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -2600,6 +3042,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2611,6 +3059,8 @@
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -2634,6 +3084,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -2657,6 +3113,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -2680,6 +3142,12 @@
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2691,6 +3159,8 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -2715,6 +3185,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2738,6 +3214,12 @@
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -2761,6 +3243,12 @@
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2784,6 +3272,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2795,6 +3289,8 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -2818,6 +3314,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -2841,6 +3343,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2852,6 +3360,8 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -2875,6 +3385,12 @@
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -2898,6 +3414,12 @@
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -2921,6 +3443,12 @@
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2932,6 +3460,8 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -2955,17 +3485,23 @@
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2981,6 +3517,24 @@
       <formula1>"WAF_v2,Standard_v2"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/assets/aks-landing-zone-checklist.xlsx
+++ b/docs/assets/aks-landing-zone-checklist.xlsx
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>App Gateway for Containers subnet (delegated, min /24). Used only when 11p = true.</t>
+          <t>App Gateway for Containers subnet (delegated, min /24). Used only when 11g = true.</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Application Gateway + WAF in front of the cluster.</t>
+          <t>Application Gateway + WAF in front of the cluster. Classic L7 ingress. Choose this OR App Gateway for Containers (11g) — not both.</t>
         </is>
       </c>
       <c r="D55" s="18" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>11p</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Application Gateway for Containers (ALB). Provisions delegated subnet 5h and ALB Controller.</t>
+          <t>Application Gateway for Containers (ALB) — next-gen L7 ingress. Provisions delegated subnet 5h and ALB Controller. Choose this OR Application Gateway WAF (11f) — not both.</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
@@ -2683,7 +2683,7 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>11i</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -2717,7 +2717,7 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>11i</t>
+          <t>11j</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>11j</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>11k</t>
+          <t>11l</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>11l</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>11n</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -2887,7 +2887,7 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>11n</t>
+          <t>11o</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>11o</t>
+          <t>11p</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">

--- a/docs/assets/aks-landing-zone-checklist.xlsx
+++ b/docs/assets/aks-landing-zone-checklist.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2392,17 +2392,17 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>11f</t>
+          <t>11e2</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>enable_app_gateway</t>
+          <t>grafana_public_access</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
+          <t>Public network access to Managed Grafana. Recommended false (private via private endpoint); a Grafana private endpoint + private DNS zone are created automatically when private endpoints are enabled.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
@@ -2426,27 +2426,27 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>11f2</t>
+          <t>11f</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>ingress_controller</t>
+          <t>enable_app_gateway</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
+          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>istio | traefik | manual</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>traefik  (istio when enable_istio is true)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
@@ -2460,27 +2460,27 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>11f3</t>
+          <t>11f2</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>appgw_tls_key_vault_secret_id</t>
+          <t>ingress_controller</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Optional. Key Vault secret ID of the TLS certificate for the Application Gateway HTTPS:443 listener (also adds an HTTP→HTTPS redirect). The gateway reads it with the AKS identity. Leave blank to serve HTTP:80 only; you can add TLS later.</t>
+          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Key Vault secret URI, or blank</t>
+          <t>istio | traefik | manual</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>(blank = HTTP:80 only)</t>
+          <t>traefik  (istio when enable_istio is true)</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
@@ -2494,27 +2494,27 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>11p</t>
+          <t>11f3</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>enable_agc</t>
+          <t>appgw_tls_key_vault_secret_id</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
+          <t>Optional. Key Vault secret ID of the TLS certificate for the Application Gateway HTTPS:443 listener (also adds an HTTP→HTTPS redirect). The gateway reads it with the AKS identity. Leave blank to serve HTTP:80 only; you can add TLS later.</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
+          <t>Key Vault secret URI, or blank</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>(blank = HTTP:80 only)</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
@@ -2528,17 +2528,17 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11p</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>enable_keda</t>
+          <t>enable_agc</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
+          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
@@ -2562,17 +2562,17 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>enable_vpa</t>
+          <t>enable_keda</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Auto-adjusts CPU and memory requests for pods.</t>
+          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
@@ -2596,17 +2596,17 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>11i</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>enable_node_auto_provisioning</t>
+          <t>enable_vpa</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
+          <t>Auto-adjusts CPU and memory requests for pods.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
@@ -2630,17 +2630,17 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>11j</t>
+          <t>11i</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>enable_istio</t>
+          <t>enable_node_auto_provisioning</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
+          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
@@ -2664,17 +2664,17 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>11k</t>
+          <t>11j</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>enable_flux</t>
+          <t>enable_istio</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
+          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
@@ -2698,17 +2698,17 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>11l</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>enable_dapr</t>
+          <t>enable_flux</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
+          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
@@ -2732,17 +2732,17 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>11l</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>enable_fips</t>
+          <t>enable_dapr</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
+          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
@@ -2766,17 +2766,17 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>11n</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>enable_backup</t>
+          <t>enable_fips</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Azure Backup for cluster resources and persistent volumes.</t>
+          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
@@ -2800,17 +2800,17 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>11o</t>
+          <t>11n</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>enable_cost_analysis</t>
+          <t>enable_backup</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Cost breakdown per namespace in the Azure portal.</t>
+          <t>Azure Backup for cluster resources and persistent volumes.</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
@@ -2830,6 +2830,40 @@
         </is>
       </c>
       <c r="H69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>11o</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>enable_cost_analysis</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Cost breakdown per namespace in the Azure portal.</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2847,7 +2881,7 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B31:H31"/>
   </mergeCells>
-  <dataValidations count="27">
+  <dataValidations count="28">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"single_region_baseline,multi_region_baseline,single_region_regulated,multi_region_regulated"</formula1>
     </dataValidation>
@@ -2897,10 +2931,10 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"istio,traefik,manual"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
@@ -2927,6 +2961,9 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2985,6 +3022,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/assets/aks-landing-zone-checklist.xlsx
+++ b/docs/assets/aks-landing-zone-checklist.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
+          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — set up and auto-wired for you; auto-selected when Istio 11j is on) or manual (baseline only — you install and wire your own open-source ingress controller). Only istio is wired by the CD pipeline; manual leaves the ingress controller and backend-pool wiring to you.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>istio | traefik | manual</t>
+          <t>istio | manual</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>traefik  (istio when enable_istio is true)</t>
+          <t>manual  (istio when enable_istio is true)</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
@@ -2864,6 +2864,40 @@
         </is>
       </c>
       <c r="H70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>11p</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>auto_scaler_profile</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Day-2 (optional): fine-tune the cluster autoscaler for cost vs performance. Keep AKS defaults unless Azure Advisor flags idle nodes. See docs.</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults | tune in tfvars</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2934,7 +2968,7 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"istio,traefik,manual"</formula1>
+      <formula1>"istio,manual"</formula1>
     </dataValidation>
     <dataValidation sqref="F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
@@ -3023,6 +3057,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
